--- a/artfynd/A 34474-2025 artfynd.xlsx
+++ b/artfynd/A 34474-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,9 +803,116 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136534708</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99366</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Z969 Borgvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>551484</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7034410</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136534708</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34474-2025 artfynd.xlsx
+++ b/artfynd/A 34474-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>136534708</v>
       </c>
       <c r="B3" t="n">
-        <v>99366</v>
+        <v>99369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34474-2025 artfynd.xlsx
+++ b/artfynd/A 34474-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>136534708</v>
       </c>
       <c r="B3" t="n">
-        <v>99369</v>
+        <v>99370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34474-2025 artfynd.xlsx
+++ b/artfynd/A 34474-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>136534708</v>
       </c>
       <c r="B3" t="n">
-        <v>99370</v>
+        <v>99375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34474-2025 artfynd.xlsx
+++ b/artfynd/A 34474-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>136534708</v>
       </c>
       <c r="B3" t="n">
-        <v>99375</v>
+        <v>99377</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34474-2025 artfynd.xlsx
+++ b/artfynd/A 34474-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136534708</v>
+        <v>136931632</v>
       </c>
       <c r="B3" t="n">
-        <v>99377</v>
+        <v>99270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,37 +816,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Z969 Borgvattnet, Ång</t>
+          <t>Björkhöjden, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551484</v>
+        <v>551588</v>
       </c>
       <c r="R3" t="n">
-        <v>7034410</v>
+        <v>7034367</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,12 +878,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,28 +892,250 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136931632</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136534708</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99377</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Z969 Borgvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>551484</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7034410</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Väg och Miljö AB</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Väg och Miljö AB, Björn Almkvist</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136534708</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136931631</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99377</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Björkhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>551602</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7034365</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136931631</t>
         </is>
       </c>
     </row>
@@ -913,6 +1143,8 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34474-2025 artfynd.xlsx
+++ b/artfynd/A 34474-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>136931632</v>
       </c>
       <c r="B3" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136534708</v>
       </c>
       <c r="B4" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136931631</v>
       </c>
       <c r="B5" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34474-2025 artfynd.xlsx
+++ b/artfynd/A 34474-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>136931632</v>
       </c>
       <c r="B3" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136534708</v>
       </c>
       <c r="B4" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136931631</v>
       </c>
       <c r="B5" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34474-2025 artfynd.xlsx
+++ b/artfynd/A 34474-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>136931632</v>
       </c>
       <c r="B3" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136534708</v>
       </c>
       <c r="B4" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136931631</v>
       </c>
       <c r="B5" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34474-2025 artfynd.xlsx
+++ b/artfynd/A 34474-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>136931632</v>
       </c>
       <c r="B3" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136534708</v>
       </c>
       <c r="B4" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136931631</v>
       </c>
       <c r="B5" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34474-2025 artfynd.xlsx
+++ b/artfynd/A 34474-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>136931632</v>
       </c>
       <c r="B3" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136534708</v>
       </c>
       <c r="B4" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136931631</v>
       </c>
       <c r="B5" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34474-2025 artfynd.xlsx
+++ b/artfynd/A 34474-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>136931632</v>
       </c>
       <c r="B3" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136534708</v>
       </c>
       <c r="B4" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136931631</v>
       </c>
       <c r="B5" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34474-2025 artfynd.xlsx
+++ b/artfynd/A 34474-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>136931632</v>
       </c>
       <c r="B3" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136534708</v>
       </c>
       <c r="B4" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136931631</v>
       </c>
       <c r="B5" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34474-2025 artfynd.xlsx
+++ b/artfynd/A 34474-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>136931632</v>
       </c>
       <c r="B3" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136534708</v>
       </c>
       <c r="B4" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136931631</v>
       </c>
       <c r="B5" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34474-2025 artfynd.xlsx
+++ b/artfynd/A 34474-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>136931632</v>
       </c>
       <c r="B3" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136534708</v>
       </c>
       <c r="B4" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136931631</v>
       </c>
       <c r="B5" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34474-2025 artfynd.xlsx
+++ b/artfynd/A 34474-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>136931632</v>
       </c>
       <c r="B3" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136931631</v>
       </c>
       <c r="B5" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34474-2025 artfynd.xlsx
+++ b/artfynd/A 34474-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>136931632</v>
       </c>
       <c r="B3" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136931631</v>
       </c>
       <c r="B5" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34474-2025 artfynd.xlsx
+++ b/artfynd/A 34474-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>136931632</v>
       </c>
       <c r="B3" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136931631</v>
       </c>
       <c r="B5" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34474-2025 artfynd.xlsx
+++ b/artfynd/A 34474-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>136931632</v>
       </c>
       <c r="B3" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136931631</v>
       </c>
       <c r="B5" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34474-2025 artfynd.xlsx
+++ b/artfynd/A 34474-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>136931632</v>
       </c>
       <c r="B3" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136931631</v>
       </c>
       <c r="B5" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34474-2025 artfynd.xlsx
+++ b/artfynd/A 34474-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>136931632</v>
       </c>
       <c r="B3" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136931631</v>
       </c>
       <c r="B5" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34474-2025 artfynd.xlsx
+++ b/artfynd/A 34474-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>136931632</v>
       </c>
       <c r="B3" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136931631</v>
       </c>
       <c r="B5" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34474-2025 artfynd.xlsx
+++ b/artfynd/A 34474-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>136931632</v>
       </c>
       <c r="B3" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136931631</v>
       </c>
       <c r="B5" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34474-2025 artfynd.xlsx
+++ b/artfynd/A 34474-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>136931632</v>
       </c>
       <c r="B3" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136931631</v>
       </c>
       <c r="B5" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34474-2025 artfynd.xlsx
+++ b/artfynd/A 34474-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>136931632</v>
       </c>
       <c r="B3" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136931631</v>
       </c>
       <c r="B5" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34474-2025 artfynd.xlsx
+++ b/artfynd/A 34474-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>136931632</v>
       </c>
       <c r="B3" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136931631</v>
       </c>
       <c r="B5" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
